--- a/project1/chart_make_over/make_over_1/pithambar_chart_make_over.xlsx
+++ b/project1/chart_make_over/make_over_1/pithambar_chart_make_over.xlsx
@@ -1,54 +1,454 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Improved Chart" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Improved Chart" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>Country/Region</t>
+  </si>
+  <si>
+    <t>Estimated Share (%)</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>U.S.</t>
+  </si>
+  <si>
+    <t>EEA</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>Values are approximate estimates read from the supplied pie chart, not original data.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -57,246 +457,694 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="FFD9E2F3"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="110"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="10"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t>Share by Country/Region (Estimated)</a:t>
             </a:r>
           </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Improved Chart'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Improved Chart'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Estimated Share (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="95000"/>
+                  <a:satMod val="105000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Improved Chart'!$A$2:$A$8</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Improved Chart'!$B$2:$B$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="35"/>
-          <min val="0"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="1"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="0"/>
+                <c15:leaderLines/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Improved Chart'!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Other</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>China</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>U.S.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>EEA</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>India</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Japan</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Russia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Improved Chart'!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0"%"</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="7.5"/>
+          <c:min val="0.5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Share (%)</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:t>Country/Region</a:t>
                 </a:r>
               </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0&quot;%&quot;" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{ecb9f6c1-dd94-46af-88f8-5936087a1f13}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="3060000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5760000" cy="2953320"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6705600" y="624840"/>
+        <a:ext cx="5759450" cy="2952750"/>
+      </xdr:xfrm>
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -578,127 +1426,98 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Country/Region</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Estimated Share (%)</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="2" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
         <v>31.5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
         <v>29.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>U.S.</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EEA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
+    <row r="6" spans="1:2">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B6" s="3">
+        <v>6</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
+    <row r="8" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Note:</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Values are approximate estimates read from the supplied pie chart, not original data.</t>
-        </is>
+    <row r="10" ht="30" customHeight="1" spans="1:2">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B10:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>